--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>98008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566642.9116544737</v>
+        <v>566643</v>
       </c>
       <c r="R2" t="n">
-        <v>6871694.961446223</v>
+        <v>6871695</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,19 +748,9 @@
           <t>1991-06-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566642.9116544737</v>
+        <v>566643</v>
       </c>
       <c r="R3" t="n">
-        <v>6871694.961446223</v>
+        <v>6871695</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1991-06-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1991-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>97792</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566642.9116544737</v>
+        <v>566643</v>
       </c>
       <c r="R4" t="n">
-        <v>6871694.961446223</v>
+        <v>6871695</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1005,19 +970,9 @@
           <t>1991-06-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1991-06-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566642.9116544737</v>
+        <v>566643</v>
       </c>
       <c r="R5" t="n">
-        <v>6871694.961446223</v>
+        <v>6871695</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1131,19 +1081,9 @@
           <t>1991-06-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1991-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566642.9116544737</v>
+        <v>566643</v>
       </c>
       <c r="R6" t="n">
-        <v>6871694.961446223</v>
+        <v>6871695</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1257,19 +1192,9 @@
           <t>1991-06-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1991-06-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100299</v>
+        <v>100305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97652</v>
+        <v>97658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100079</v>
+        <v>100085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100305</v>
+        <v>100309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97658</v>
+        <v>97660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100085</v>
+        <v>100089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100309</v>
+        <v>100315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100089</v>
+        <v>100095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100315</v>
+        <v>100316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97660</v>
+        <v>97661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100095</v>
+        <v>100096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100316</v>
+        <v>100343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97661</v>
+        <v>97688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100096</v>
+        <v>100123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100343</v>
+        <v>100349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97688</v>
+        <v>97694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100123</v>
+        <v>100129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100349</v>
+        <v>100356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97694</v>
+        <v>97701</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100129</v>
+        <v>100136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100356</v>
+        <v>100360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97701</v>
+        <v>97705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100136</v>
+        <v>100140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100360</v>
+        <v>100367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97705</v>
+        <v>97712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100140</v>
+        <v>100147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100370</v>
+        <v>100375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97715</v>
+        <v>97720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100150</v>
+        <v>100155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23964-2025 artfynd.xlsx
+++ b/artfynd/A 23964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82375909</v>
       </c>
       <c r="B2" t="n">
-        <v>100375</v>
+        <v>100383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82375918</v>
       </c>
       <c r="B3" t="n">
-        <v>97720</v>
+        <v>97728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82375910</v>
       </c>
       <c r="B4" t="n">
-        <v>100155</v>
+        <v>100163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82375908</v>
       </c>
       <c r="B5" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82375923</v>
       </c>
       <c r="B6" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
